--- a/DGWJ001‐1.xlsx
+++ b/DGWJ001‐1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\go\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2211984-6041-47A9-B97F-1C0B6C72EC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BAABBE-0822-4070-B000-BFECC12AB221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="27">
   <si>
     <t>発送日</t>
     <rPh sb="0" eb="3">
@@ -145,6 +145,74 @@
   </si>
   <si>
     <t>ポケモンテラスタル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>振込先：</t>
+    <rPh sb="0" eb="2">
+      <t>フリコミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>みずほ銀行</t>
+    <rPh sb="3" eb="5">
+      <t>ギンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>普通口座：</t>
+    <rPh sb="0" eb="2">
+      <t>フツウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大塚支店：</t>
+    <rPh sb="0" eb="2">
+      <t>オオツカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名義：</t>
+    <rPh sb="0" eb="2">
+      <t>メイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オウ　グン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>請求明細</t>
+    <rPh sb="0" eb="2">
+      <t>セイキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>請求金額：</t>
+    <rPh sb="0" eb="2">
+      <t>セイキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キンガク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -155,7 +223,7 @@
   <numFmts count="1">
     <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,8 +247,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +273,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -268,6 +351,23 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="5" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -548,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:N13"/>
+  <dimension ref="C2:N20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="15.08203125" customWidth="1"/>
@@ -557,276 +657,322 @@
     <col min="12" max="12" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14">
-      <c r="N1" s="9"/>
-    </row>
-    <row r="2" spans="3:14" ht="20">
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="3:14">
+      <c r="C2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="15"/>
+    </row>
+    <row r="3" spans="3:14">
+      <c r="C3" s="13"/>
+      <c r="D3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="16">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="3:14">
+      <c r="C4" s="13"/>
+      <c r="D4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="16">
+        <v>2339583</v>
+      </c>
+    </row>
+    <row r="5" spans="3:14">
+      <c r="C5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="3:14">
+      <c r="C6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="17">
+        <f>SUM(H10:I20)</f>
+        <v>749990</v>
+      </c>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="8" spans="3:14">
+      <c r="C8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="9"/>
+    </row>
+    <row r="9" spans="3:14" ht="20">
+      <c r="C9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E9" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F9" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I9" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="3:14">
-      <c r="C3" s="2">
+    <row r="10" spans="3:14">
+      <c r="C10" s="2">
         <v>45944</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="E10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
         <v>180</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G10" s="3">
         <v>374</v>
       </c>
-      <c r="H3" s="8">
-        <f t="shared" ref="H3:H13" si="0">F3*G3</f>
+      <c r="H10" s="8">
+        <f t="shared" ref="H10:H20" si="0">F10*G10</f>
         <v>67320</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I10" s="8">
         <v>36050</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="7">
-        <f>SUM(H3:I13)</f>
-        <v>749990</v>
-      </c>
-    </row>
-    <row r="4" spans="3:14">
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G4" s="3">
-        <v>120</v>
-      </c>
-      <c r="H4" s="8">
-        <f t="shared" si="0"/>
-        <v>132000</v>
-      </c>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="3:14">
-      <c r="C5" s="2">
-        <v>45943</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G5" s="3">
-        <v>48</v>
-      </c>
-      <c r="H5" s="8">
-        <f t="shared" si="0"/>
-        <v>62400</v>
-      </c>
-      <c r="I5" s="8">
-        <v>21400</v>
-      </c>
-    </row>
-    <row r="6" spans="3:14">
-      <c r="C6" s="2">
-        <v>45936</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>180</v>
-      </c>
-      <c r="G6" s="3">
-        <v>126</v>
-      </c>
-      <c r="H6" s="8">
-        <f t="shared" si="0"/>
-        <v>22680</v>
-      </c>
-      <c r="I6" s="8">
-        <v>29600</v>
-      </c>
-    </row>
-    <row r="7" spans="3:14">
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
-        <f t="shared" si="0"/>
-        <v>8400</v>
-      </c>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="3:14">
-      <c r="C8" s="2">
-        <v>45935</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>180</v>
-      </c>
-      <c r="G8" s="3">
-        <v>160</v>
-      </c>
-      <c r="H8" s="8">
-        <f t="shared" si="0"/>
-        <v>28800</v>
-      </c>
-      <c r="I8" s="8">
-        <v>14050</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14">
-      <c r="C9" s="2"/>
-      <c r="D9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>550</v>
-      </c>
-      <c r="G9" s="3">
-        <v>15</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="0"/>
-        <v>8250</v>
-      </c>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="3:14">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1210</v>
-      </c>
-      <c r="G10" s="3">
-        <v>140</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" si="0"/>
-        <v>169400</v>
-      </c>
-      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="3:14">
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G11" s="3">
+        <v>120</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="0"/>
+        <v>132000</v>
+      </c>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="3:14">
+      <c r="C12" s="2">
+        <v>45943</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>48</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="0"/>
+        <v>62400</v>
+      </c>
+      <c r="I12" s="8">
+        <v>21400</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14">
+      <c r="C13" s="2">
+        <v>45936</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>180</v>
+      </c>
+      <c r="G13" s="3">
+        <v>126</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="0"/>
+        <v>22680</v>
+      </c>
+      <c r="I13" s="8">
+        <v>29600</v>
+      </c>
+    </row>
+    <row r="14" spans="3:14">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="0"/>
+        <v>8400</v>
+      </c>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="3:14">
+      <c r="C15" s="2">
+        <v>45935</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>180</v>
+      </c>
+      <c r="G15" s="3">
+        <v>160</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="0"/>
+        <v>28800</v>
+      </c>
+      <c r="I15" s="8">
+        <v>14050</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14">
+      <c r="C16" s="2"/>
+      <c r="D16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>550</v>
+      </c>
+      <c r="G16" s="3">
+        <v>15</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="0"/>
+        <v>8250</v>
+      </c>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="3:9">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1210</v>
+      </c>
+      <c r="G17" s="3">
+        <v>140</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="0"/>
+        <v>169400</v>
+      </c>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="3:9">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F18" s="3">
         <v>1375</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G18" s="3">
         <v>48</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H18" s="8">
         <f t="shared" si="0"/>
         <v>66000</v>
       </c>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="3:14">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="3:9">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="10">
         <v>1430</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G19" s="10">
         <v>48</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
         <v>68640</v>
       </c>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="3:14">
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="3:9">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F20" s="10">
         <v>1500</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G20" s="10">
         <v>10</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H20" s="11">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="I13" s="3"/>
+      <c r="I20" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="D6:E6"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
